--- a/final_data_pipeline/output/311514longform.xlsx
+++ b/final_data_pipeline/output/311514longform.xlsx
@@ -786,7 +786,7 @@
         <v>71</v>
       </c>
       <c r="AA2">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AB2">
         <v>8000</v>
@@ -881,7 +881,7 @@
         <v>71</v>
       </c>
       <c r="AA3">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AB3">
         <v>8000</v>
@@ -970,7 +970,7 @@
         <v>71</v>
       </c>
       <c r="AA4">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AB4">
         <v>8000</v>
@@ -1059,7 +1059,7 @@
         <v>71</v>
       </c>
       <c r="AA5">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AB5">
         <v>8000</v>
@@ -1148,7 +1148,7 @@
         <v>71</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AB6">
         <v>8000</v>
@@ -1237,7 +1237,7 @@
         <v>71</v>
       </c>
       <c r="AA7">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AB7">
         <v>8000</v>
@@ -1326,7 +1326,7 @@
         <v>71</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AB8">
         <v>8000</v>
@@ -1415,7 +1415,7 @@
         <v>71</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AB9">
         <v>8000</v>
@@ -1504,7 +1504,7 @@
         <v>71</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AB10">
         <v>8000</v>
@@ -1593,7 +1593,7 @@
         <v>71</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AB11">
         <v>8000</v>
@@ -1688,7 +1688,7 @@
         <v>71</v>
       </c>
       <c r="AA12">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AB12">
         <v>8000</v>
@@ -1777,7 +1777,7 @@
         <v>71</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AB13">
         <v>8000</v>
@@ -1866,7 +1866,7 @@
         <v>71</v>
       </c>
       <c r="AA14">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AB14">
         <v>8000</v>
@@ -1955,7 +1955,7 @@
         <v>71</v>
       </c>
       <c r="AA15">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AB15">
         <v>8000</v>
@@ -2044,7 +2044,7 @@
         <v>71</v>
       </c>
       <c r="AA16">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AB16">
         <v>8000</v>
@@ -3943,7 +3943,7 @@
         <v>71</v>
       </c>
       <c r="AA37">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AB37">
         <v>8000</v>
@@ -4038,7 +4038,7 @@
         <v>71</v>
       </c>
       <c r="AA38">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AB38">
         <v>8000</v>
@@ -4133,7 +4133,7 @@
         <v>71</v>
       </c>
       <c r="AA39">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AB39">
         <v>8000</v>
@@ -4222,7 +4222,7 @@
         <v>71</v>
       </c>
       <c r="AA40">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AB40">
         <v>8000</v>
@@ -4311,7 +4311,7 @@
         <v>71</v>
       </c>
       <c r="AA41">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AB41">
         <v>8000</v>
@@ -4400,7 +4400,7 @@
         <v>71</v>
       </c>
       <c r="AA42">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AB42">
         <v>8000</v>
@@ -4489,7 +4489,7 @@
         <v>71</v>
       </c>
       <c r="AA43">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AB43">
         <v>8000</v>
@@ -4578,7 +4578,7 @@
         <v>71</v>
       </c>
       <c r="AA44">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AB44">
         <v>8000</v>
@@ -4667,7 +4667,7 @@
         <v>71</v>
       </c>
       <c r="AA45">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AB45">
         <v>8000</v>
@@ -4756,7 +4756,7 @@
         <v>71</v>
       </c>
       <c r="AA46">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AB46">
         <v>8000</v>
@@ -5296,7 +5296,7 @@
         <v>71</v>
       </c>
       <c r="AA52">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AB52">
         <v>8000</v>
@@ -5385,7 +5385,7 @@
         <v>71</v>
       </c>
       <c r="AA53">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AB53">
         <v>8000</v>
@@ -5474,7 +5474,7 @@
         <v>71</v>
       </c>
       <c r="AA54">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AB54">
         <v>8000</v>
@@ -5569,7 +5569,7 @@
         <v>71</v>
       </c>
       <c r="AA55">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AB55">
         <v>8000</v>
@@ -5658,7 +5658,7 @@
         <v>71</v>
       </c>
       <c r="AA56">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AB56">
         <v>8000</v>
@@ -5747,7 +5747,7 @@
         <v>71</v>
       </c>
       <c r="AA57">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AB57">
         <v>8000</v>
@@ -5836,7 +5836,7 @@
         <v>71</v>
       </c>
       <c r="AA58">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AB58">
         <v>8000</v>
@@ -5925,7 +5925,7 @@
         <v>71</v>
       </c>
       <c r="AA59">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AB59">
         <v>8000</v>
@@ -6014,7 +6014,7 @@
         <v>71</v>
       </c>
       <c r="AA60">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AB60">
         <v>8000</v>
@@ -6103,7 +6103,7 @@
         <v>71</v>
       </c>
       <c r="AA61">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AB61">
         <v>8000</v>
@@ -6198,7 +6198,7 @@
         <v>71</v>
       </c>
       <c r="AA62">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AB62">
         <v>8000</v>
@@ -6293,7 +6293,7 @@
         <v>71</v>
       </c>
       <c r="AA63">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AB63">
         <v>8000</v>
@@ -6382,7 +6382,7 @@
         <v>71</v>
       </c>
       <c r="AA64">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AB64">
         <v>8000</v>
@@ -6471,7 +6471,7 @@
         <v>71</v>
       </c>
       <c r="AA65">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AB65">
         <v>8000</v>
@@ -6560,7 +6560,7 @@
         <v>71</v>
       </c>
       <c r="AA66">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AB66">
         <v>8000</v>
@@ -7551,7 +7551,7 @@
         <v>71</v>
       </c>
       <c r="AA77">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB77">
         <v>8000</v>
@@ -7640,7 +7640,7 @@
         <v>71</v>
       </c>
       <c r="AA78">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB78">
         <v>8000</v>
@@ -7735,7 +7735,7 @@
         <v>71</v>
       </c>
       <c r="AA79">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB79">
         <v>8000</v>
@@ -7824,7 +7824,7 @@
         <v>71</v>
       </c>
       <c r="AA80">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB80">
         <v>8000</v>
@@ -7913,7 +7913,7 @@
         <v>71</v>
       </c>
       <c r="AA81">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB81">
         <v>8000</v>
@@ -8453,7 +8453,7 @@
         <v>71</v>
       </c>
       <c r="AA87">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB87">
         <v>8000</v>
@@ -8542,7 +8542,7 @@
         <v>71</v>
       </c>
       <c r="AA88">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB88">
         <v>8000</v>
@@ -8637,7 +8637,7 @@
         <v>71</v>
       </c>
       <c r="AA89">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB89">
         <v>8000</v>
@@ -8726,7 +8726,7 @@
         <v>71</v>
       </c>
       <c r="AA90">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB90">
         <v>8000</v>
@@ -8815,7 +8815,7 @@
         <v>71</v>
       </c>
       <c r="AA91">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB91">
         <v>8000</v>
